--- a/evaluation/multiple_choice_qa/MMLU-clinical_knowledge/qwen2.5_trained/fa_qwn_result.xlsx
+++ b/evaluation/multiple_choice_qa/MMLU-clinical_knowledge/qwen2.5_trained/fa_qwn_result.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29311"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1622F83-FE63-4A1A-8330-25BA480FBB9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB311DFE-9E6F-4365-B31B-9311745C62F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,6 +179,9 @@
 گزینه [D] بیمار اوروستومی دارد، این گزینه صحیح نیست، زیرا اوروستومی معمولاً با کیسه باز (open pouch) و نه کیسه بسته (closed pouch) کار می‌کند.</t>
   </si>
   <si>
+    <t>invalid</t>
+  </si>
+  <si>
     <t>با افزایش تعداد دوی سرعت چه اتفاقی رخ میدهد؟</t>
   </si>
   <si>
@@ -3203,9 +3206,6 @@
   </si>
   <si>
     <t>جفت الکترون‌های FADH2 و NADH+H که در فسفریله شدن حضور دارند، می‌توانند مجموعاً حاوی انرژی آزاد کافی برای تولید 2 ATP باشد. اما در راه‌حل سلولی، این جفت الکترون‌ها عمدتاً در دی آلدوسیتریت (Dichlorophenolindophenol) یا سیگنال‌های اخلاقی (Indicators) استفاده می‌شوند تا انرژی آزاد آن‌ها را برای تولید ATP از طریق پروسس‌های مثل ترانسپورت الکترونی استفاده نشود. بنابراین، معمولاً جفت الکترون‌های FADH2 و NADH+H می‌توانند مجموعاً حاوی انرژی آزاد کافی برای تولید 2 ATP باشد، اما در مسائل مرتبط با فسفریله شدن سلولی، می‌تواند مقدار کمتری باشد.</t>
-  </si>
-  <si>
-    <t>invalid</t>
   </si>
   <si>
     <t>فیبر عضلانی زمانی شل می شود که:</t>
@@ -6761,7 +6761,7 @@
         <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -6821,24 +6821,24 @@
         <v>28</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F7" t="s">
         <v>14</v>
@@ -6846,19 +6846,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
         <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F8" t="s">
         <v>14</v>
@@ -6866,19 +6866,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s">
         <v>8</v>
@@ -6886,19 +6886,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F10" t="s">
         <v>8</v>
@@ -6906,19 +6906,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F11" t="s">
         <v>11</v>
@@ -6926,39 +6926,39 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F13" t="s">
         <v>14</v>
@@ -6966,19 +6966,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s">
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F14" t="s">
         <v>14</v>
@@ -6986,19 +6986,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
         <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F15" t="s">
         <v>14</v>
@@ -7006,19 +7006,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F16" t="s">
         <v>11</v>
@@ -7026,59 +7026,59 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
         <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F19" t="s">
         <v>11</v>
@@ -7086,19 +7086,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F20" t="s">
         <v>11</v>
@@ -7106,19 +7106,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F21" t="s">
         <v>14</v>
@@ -7126,19 +7126,19 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
         <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F22" t="s">
         <v>14</v>
@@ -7146,19 +7146,19 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C23" t="s">
         <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F23" t="s">
         <v>8</v>
@@ -7166,19 +7166,19 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B24" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C24" t="s">
         <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E24" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F24" t="s">
         <v>8</v>
@@ -7186,19 +7186,19 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C25" t="s">
         <v>11</v>
       </c>
       <c r="D25" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E25" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F25" t="s">
         <v>14</v>
@@ -7206,19 +7206,19 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B26" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
       </c>
       <c r="D26" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E26" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F26" t="s">
         <v>11</v>
@@ -7226,19 +7226,19 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B27" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
       </c>
       <c r="D27" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F27" t="s">
         <v>11</v>
@@ -7246,19 +7246,19 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B28" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C28" t="s">
         <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E28" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F28" t="s">
         <v>11</v>
@@ -7266,19 +7266,19 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B29" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C29" t="s">
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E29" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F29" t="s">
         <v>11</v>
@@ -7286,39 +7286,39 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B30" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
       </c>
       <c r="D30" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E30" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B31" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C31" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D31" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E31" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F31" t="s">
         <v>14</v>
@@ -7326,79 +7326,79 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E32" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C33" t="s">
         <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E33" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F33" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B34" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C34" t="s">
         <v>8</v>
       </c>
       <c r="D34" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E34" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F34" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B35" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C35" t="s">
         <v>11</v>
       </c>
       <c r="D35" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F35" t="s">
         <v>14</v>
@@ -7406,19 +7406,19 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B36" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C36" t="s">
         <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E36" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F36" t="s">
         <v>11</v>
@@ -7426,19 +7426,19 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B37" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C37" t="s">
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E37" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F37" t="s">
         <v>14</v>
@@ -7446,39 +7446,39 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B38" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C38" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D38" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E38" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F38" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B39" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C39" t="s">
         <v>11</v>
       </c>
       <c r="D39" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E39" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F39" t="s">
         <v>8</v>
@@ -7486,19 +7486,19 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C40" t="s">
         <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E40" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F40" t="s">
         <v>11</v>
@@ -7506,19 +7506,19 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B41" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C41" t="s">
         <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E41" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F41" t="s">
         <v>11</v>
@@ -7526,19 +7526,19 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B42" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C42" t="s">
         <v>11</v>
       </c>
       <c r="D42" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E42" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F42" t="s">
         <v>11</v>
@@ -7546,19 +7546,19 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B43" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C43" t="s">
         <v>14</v>
       </c>
       <c r="D43" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E43" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F43" t="s">
         <v>14</v>
@@ -7566,39 +7566,39 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B44" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C44" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D44" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E44" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F44" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B45" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C45" t="s">
         <v>11</v>
       </c>
       <c r="D45" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E45" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F45" t="s">
         <v>11</v>
@@ -7606,19 +7606,19 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B46" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C46" t="s">
         <v>14</v>
       </c>
       <c r="D46" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E46" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F46" t="s">
         <v>11</v>
@@ -7626,19 +7626,19 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B47" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C47" t="s">
         <v>14</v>
       </c>
       <c r="D47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E47" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F47" t="s">
         <v>11</v>
@@ -7646,19 +7646,19 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B48" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C48" t="s">
         <v>14</v>
       </c>
       <c r="D48" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E48" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F48" t="s">
         <v>14</v>
@@ -7666,19 +7666,19 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B49" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C49" t="s">
         <v>8</v>
       </c>
       <c r="D49" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E49" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F49" t="s">
         <v>8</v>
@@ -7686,19 +7686,19 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B50" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C50" t="s">
         <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E50" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F50" t="s">
         <v>8</v>
@@ -7706,19 +7706,19 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B51" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C51" t="s">
         <v>14</v>
       </c>
       <c r="D51" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E51" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F51" t="s">
         <v>14</v>
@@ -7726,79 +7726,79 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B52" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C52" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D52" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E52" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F52" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B53" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C53" t="s">
         <v>8</v>
       </c>
       <c r="D53" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E53" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F53" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B54" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C54" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D54" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E54" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F54" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B55" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C55" t="s">
         <v>11</v>
       </c>
       <c r="D55" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E55" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F55" t="s">
         <v>14</v>
@@ -7806,19 +7806,19 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B56" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
       </c>
       <c r="D56" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E56" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F56" t="s">
         <v>14</v>
@@ -7826,79 +7826,79 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B57" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E57" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F57" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B58" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C58" t="s">
         <v>11</v>
       </c>
       <c r="D58" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E58" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F58" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B59" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C59" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D59" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E59" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F59" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B60" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C60" t="s">
         <v>14</v>
       </c>
       <c r="D60" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E60" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F60" t="s">
         <v>14</v>
@@ -7906,19 +7906,19 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B61" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C61" t="s">
         <v>11</v>
       </c>
       <c r="D61" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E61" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F61" t="s">
         <v>11</v>
@@ -7926,39 +7926,39 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B62" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C62" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D62" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E62" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F62" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B63" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C63" t="s">
         <v>11</v>
       </c>
       <c r="D63" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E63" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F63" t="s">
         <v>11</v>
@@ -7966,99 +7966,99 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B64" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C64" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D64" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E64" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F64" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B65" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
       </c>
       <c r="D65" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E65" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F65" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B66" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C66" t="s">
         <v>8</v>
       </c>
       <c r="D66" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E66" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F66" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B67" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C67" t="s">
         <v>14</v>
       </c>
       <c r="D67" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E67" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F67" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B68" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C68" t="s">
         <v>11</v>
       </c>
       <c r="D68" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E68" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F68" t="s">
         <v>11</v>
@@ -8066,19 +8066,19 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B69" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C69" t="s">
         <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E69" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F69" t="s">
         <v>14</v>
@@ -8086,19 +8086,19 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B70" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C70" t="s">
         <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E70" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F70" t="s">
         <v>14</v>
@@ -8106,19 +8106,19 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B71" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C71" t="s">
         <v>14</v>
       </c>
       <c r="D71" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E71" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F71" t="s">
         <v>14</v>
@@ -8126,39 +8126,39 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B72" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C72" t="s">
         <v>8</v>
       </c>
       <c r="D72" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E72" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F72" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B73" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C73" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D73" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E73" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F73" t="s">
         <v>11</v>
@@ -8166,39 +8166,39 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B74" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C74" t="s">
         <v>14</v>
       </c>
       <c r="D74" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E74" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F74" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B75" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C75" t="s">
         <v>14</v>
       </c>
       <c r="D75" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E75" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F75" t="s">
         <v>11</v>
@@ -8206,39 +8206,39 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B76" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
       </c>
       <c r="D76" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E76" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F76" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B77" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C77" t="s">
         <v>11</v>
       </c>
       <c r="D77" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E77" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F77" t="s">
         <v>11</v>
@@ -8246,19 +8246,19 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B78" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C78" t="s">
         <v>11</v>
       </c>
       <c r="D78" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E78" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F78" t="s">
         <v>11</v>
@@ -8266,19 +8266,19 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B79" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C79" t="s">
         <v>8</v>
       </c>
       <c r="D79" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E79" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F79" t="s">
         <v>8</v>
@@ -8286,19 +8286,19 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B80" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C80" t="s">
         <v>11</v>
       </c>
       <c r="D80" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E80" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F80" t="s">
         <v>11</v>
@@ -8306,19 +8306,19 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B81" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C81" t="s">
         <v>11</v>
       </c>
       <c r="D81" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E81" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F81" t="s">
         <v>8</v>
@@ -8326,19 +8326,19 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B82" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C82" t="s">
         <v>14</v>
       </c>
       <c r="D82" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E82" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F82" t="s">
         <v>8</v>
@@ -8346,19 +8346,19 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B83" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C83" t="s">
         <v>14</v>
       </c>
       <c r="D83" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E83" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F83" t="s">
         <v>8</v>
@@ -8366,19 +8366,19 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B84" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C84" t="s">
         <v>11</v>
       </c>
       <c r="D84" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E84" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F84" t="s">
         <v>8</v>
@@ -8386,19 +8386,19 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B85" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C85" t="s">
         <v>11</v>
       </c>
       <c r="D85" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E85" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F85" t="s">
         <v>14</v>
@@ -8406,19 +8406,19 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B86" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C86" t="s">
         <v>14</v>
       </c>
       <c r="D86" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E86" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F86" t="s">
         <v>14</v>
@@ -8426,19 +8426,19 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B87" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C87" t="s">
         <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E87" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F87" t="s">
         <v>14</v>
@@ -8446,19 +8446,19 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B88" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C88" t="s">
         <v>8</v>
       </c>
       <c r="D88" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E88" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F88" t="s">
         <v>11</v>
@@ -8466,19 +8466,19 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B89" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C89" t="s">
         <v>11</v>
       </c>
       <c r="D89" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E89" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F89" t="s">
         <v>14</v>
@@ -8486,19 +8486,19 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B90" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C90" t="s">
         <v>14</v>
       </c>
       <c r="D90" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E90" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F90" t="s">
         <v>14</v>
@@ -8506,19 +8506,19 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B91" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C91" t="s">
         <v>14</v>
       </c>
       <c r="D91" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E91" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F91" t="s">
         <v>14</v>
@@ -8526,59 +8526,59 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B92" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C92" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D92" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E92" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F92" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B93" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C93" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D93" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E93" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F93" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B94" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C94" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D94" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E94" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F94" t="s">
         <v>8</v>
@@ -8586,19 +8586,19 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B95" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C95" t="s">
         <v>14</v>
       </c>
       <c r="D95" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E95" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F95" t="s">
         <v>14</v>
@@ -8606,79 +8606,79 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B96" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C96" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D96" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E96" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F96" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B97" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C97" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D97" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E97" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F97" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B98" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C98" t="s">
         <v>14</v>
       </c>
       <c r="D98" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E98" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F98" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B99" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C99" t="s">
         <v>8</v>
       </c>
       <c r="D99" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E99" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F99" t="s">
         <v>8</v>
@@ -8686,19 +8686,19 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B100" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C100" t="s">
         <v>11</v>
       </c>
       <c r="D100" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E100" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F100" t="s">
         <v>11</v>
@@ -8706,79 +8706,79 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B101" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C101" t="s">
         <v>11</v>
       </c>
       <c r="D101" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E101" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F101" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B102" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C102" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D102" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E102" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F102" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B103" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C103" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D103" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E103" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F103" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B104" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C104" t="s">
         <v>11</v>
       </c>
       <c r="D104" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E104" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F104" t="s">
         <v>11</v>
@@ -8786,39 +8786,39 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B105" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C105" t="s">
         <v>11</v>
       </c>
       <c r="D105" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E105" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F105" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B106" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C106" t="s">
         <v>14</v>
       </c>
       <c r="D106" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E106" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F106" t="s">
         <v>14</v>
@@ -8826,19 +8826,19 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B107" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C107" t="s">
         <v>14</v>
       </c>
       <c r="D107" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E107" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F107" t="s">
         <v>11</v>
@@ -8846,19 +8846,19 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B108" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C108" t="s">
         <v>14</v>
       </c>
       <c r="D108" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E108" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F108" t="s">
         <v>14</v>
@@ -8866,19 +8866,19 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B109" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C109" t="s">
         <v>8</v>
       </c>
       <c r="D109" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E109" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F109" t="s">
         <v>8</v>
@@ -8886,19 +8886,19 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B110" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C110" t="s">
         <v>14</v>
       </c>
       <c r="D110" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E110" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F110" t="s">
         <v>8</v>
@@ -8906,19 +8906,19 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B111" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C111" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D111" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E111" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F111" t="s">
         <v>11</v>
@@ -8926,59 +8926,59 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B112" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C112" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D112" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E112" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F112" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B113" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C113" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D113" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E113" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F113" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B114" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C114" t="s">
         <v>14</v>
       </c>
       <c r="D114" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E114" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F114" t="s">
         <v>14</v>
@@ -8986,19 +8986,19 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B115" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C115" t="s">
         <v>8</v>
       </c>
       <c r="D115" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E115" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F115" t="s">
         <v>14</v>
@@ -9006,39 +9006,39 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B116" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C116" t="s">
         <v>8</v>
       </c>
       <c r="D116" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E116" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F116" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B117" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C117" t="s">
         <v>8</v>
       </c>
       <c r="D117" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E117" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F117" t="s">
         <v>8</v>
@@ -9046,19 +9046,19 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B118" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C118" t="s">
         <v>14</v>
       </c>
       <c r="D118" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E118" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F118" t="s">
         <v>14</v>
@@ -9066,19 +9066,19 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B119" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C119" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D119" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E119" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F119" t="s">
         <v>8</v>
@@ -9086,19 +9086,19 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B120" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C120" t="s">
         <v>11</v>
       </c>
       <c r="D120" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E120" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F120" t="s">
         <v>14</v>
@@ -9106,19 +9106,19 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B121" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C121" t="s">
         <v>14</v>
       </c>
       <c r="D121" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E121" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F121" t="s">
         <v>11</v>
@@ -9126,19 +9126,19 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B122" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C122" t="s">
         <v>11</v>
       </c>
       <c r="D122" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E122" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F122" t="s">
         <v>11</v>
@@ -9146,19 +9146,19 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B123" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C123" t="s">
         <v>8</v>
       </c>
       <c r="D123" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E123" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F123" t="s">
         <v>8</v>
@@ -9166,19 +9166,19 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B124" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C124" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D124" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E124" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F124" t="s">
         <v>11</v>
@@ -9186,19 +9186,19 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B125" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C125" t="s">
         <v>14</v>
       </c>
       <c r="D125" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E125" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F125" t="s">
         <v>8</v>
@@ -9206,19 +9206,19 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B126" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C126" t="s">
         <v>8</v>
       </c>
       <c r="D126" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E126" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F126" t="s">
         <v>8</v>
@@ -9226,19 +9226,19 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B127" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C127" t="s">
         <v>14</v>
       </c>
       <c r="D127" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E127" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F127" t="s">
         <v>14</v>
@@ -9246,19 +9246,19 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B128" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C128" t="s">
         <v>8</v>
       </c>
       <c r="D128" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E128" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F128" t="s">
         <v>8</v>
@@ -9266,19 +9266,19 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B129" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C129" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D129" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E129" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F129" t="s">
         <v>8</v>
@@ -9286,19 +9286,19 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B130" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C130" t="s">
         <v>8</v>
       </c>
       <c r="D130" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E130" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F130" t="s">
         <v>11</v>
@@ -9306,22 +9306,22 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B131" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C131" t="s">
         <v>11</v>
       </c>
       <c r="D131" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E131" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F131" t="s">
-        <v>529</v>
+        <v>29</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -9412,7 +9412,7 @@
         <v>547</v>
       </c>
       <c r="C136" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D136" t="s">
         <v>548</v>
@@ -9432,7 +9432,7 @@
         <v>551</v>
       </c>
       <c r="C137" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D137" t="s">
         <v>552</v>
@@ -9441,7 +9441,7 @@
         <v>553</v>
       </c>
       <c r="F137" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -9461,7 +9461,7 @@
         <v>557</v>
       </c>
       <c r="F138" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -9472,7 +9472,7 @@
         <v>559</v>
       </c>
       <c r="C139" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D139" t="s">
         <v>560</v>
@@ -9492,7 +9492,7 @@
         <v>563</v>
       </c>
       <c r="C140" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D140" t="s">
         <v>564</v>
@@ -9501,7 +9501,7 @@
         <v>565</v>
       </c>
       <c r="F140" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -9521,7 +9521,7 @@
         <v>569</v>
       </c>
       <c r="F141" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -9541,7 +9541,7 @@
         <v>573</v>
       </c>
       <c r="F142" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -9552,7 +9552,7 @@
         <v>575</v>
       </c>
       <c r="C143" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D143" t="s">
         <v>576</v>
@@ -9561,7 +9561,7 @@
         <v>577</v>
       </c>
       <c r="F143" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -9701,7 +9701,7 @@
         <v>605</v>
       </c>
       <c r="F150" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -9861,7 +9861,7 @@
         <v>637</v>
       </c>
       <c r="F158" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -9941,7 +9941,7 @@
         <v>653</v>
       </c>
       <c r="F162" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -10001,7 +10001,7 @@
         <v>665</v>
       </c>
       <c r="F165" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -10052,7 +10052,7 @@
         <v>675</v>
       </c>
       <c r="C168" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D168" t="s">
         <v>676</v>
@@ -10092,7 +10092,7 @@
         <v>683</v>
       </c>
       <c r="C170" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D170" t="s">
         <v>684</v>
@@ -10101,7 +10101,7 @@
         <v>685</v>
       </c>
       <c r="F170" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -10121,7 +10121,7 @@
         <v>689</v>
       </c>
       <c r="F171" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -10152,7 +10152,7 @@
         <v>695</v>
       </c>
       <c r="C173" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D173" t="s">
         <v>696</v>
@@ -10161,7 +10161,7 @@
         <v>697</v>
       </c>
       <c r="F173" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -10241,7 +10241,7 @@
         <v>713</v>
       </c>
       <c r="F177" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -10252,7 +10252,7 @@
         <v>715</v>
       </c>
       <c r="C178" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D178" t="s">
         <v>716</v>
@@ -10261,7 +10261,7 @@
         <v>717</v>
       </c>
       <c r="F178" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="179" spans="1:6">
@@ -10272,7 +10272,7 @@
         <v>719</v>
       </c>
       <c r="C179" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D179" t="s">
         <v>720</v>
@@ -10321,7 +10321,7 @@
         <v>729</v>
       </c>
       <c r="F181" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -10341,7 +10341,7 @@
         <v>733</v>
       </c>
       <c r="F182" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -10401,7 +10401,7 @@
         <v>745</v>
       </c>
       <c r="F185" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -10412,7 +10412,7 @@
         <v>747</v>
       </c>
       <c r="C186" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D186" t="s">
         <v>748</v>
@@ -10421,7 +10421,7 @@
         <v>749</v>
       </c>
       <c r="F186" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -10452,7 +10452,7 @@
         <v>755</v>
       </c>
       <c r="C188" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D188" t="s">
         <v>756</v>
@@ -10461,7 +10461,7 @@
         <v>757</v>
       </c>
       <c r="F188" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="189" spans="1:6">
@@ -10472,7 +10472,7 @@
         <v>759</v>
       </c>
       <c r="C189" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D189" t="s">
         <v>760</v>
@@ -10532,7 +10532,7 @@
         <v>771</v>
       </c>
       <c r="C192" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D192" t="s">
         <v>772</v>
@@ -10541,7 +10541,7 @@
         <v>773</v>
       </c>
       <c r="F192" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="193" spans="1:6">
@@ -10592,7 +10592,7 @@
         <v>783</v>
       </c>
       <c r="C195" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D195" t="s">
         <v>784</v>
@@ -10601,7 +10601,7 @@
         <v>785</v>
       </c>
       <c r="F195" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="196" spans="1:6">
@@ -10621,7 +10621,7 @@
         <v>789</v>
       </c>
       <c r="F196" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -10632,7 +10632,7 @@
         <v>791</v>
       </c>
       <c r="C197" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D197" t="s">
         <v>792</v>
@@ -10712,7 +10712,7 @@
         <v>807</v>
       </c>
       <c r="C201" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D201" t="s">
         <v>808</v>
@@ -10752,7 +10752,7 @@
         <v>815</v>
       </c>
       <c r="C203" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D203" t="s">
         <v>816</v>
@@ -10761,7 +10761,7 @@
         <v>817</v>
       </c>
       <c r="F203" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -10921,7 +10921,7 @@
         <v>849</v>
       </c>
       <c r="F211" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -11072,7 +11072,7 @@
         <v>879</v>
       </c>
       <c r="C219" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D219" t="s">
         <v>880</v>
@@ -11192,7 +11192,7 @@
         <v>903</v>
       </c>
       <c r="C225" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D225" t="s">
         <v>904</v>
@@ -11201,7 +11201,7 @@
         <v>905</v>
       </c>
       <c r="F225" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="226" spans="1:6">
@@ -11261,7 +11261,7 @@
         <v>917</v>
       </c>
       <c r="F228" t="s">
-        <v>529</v>
+        <v>52</v>
       </c>
     </row>
     <row r="229" spans="1:6">
@@ -11361,7 +11361,7 @@
         <v>937</v>
       </c>
       <c r="F233" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="234" spans="1:6">
@@ -11421,7 +11421,7 @@
         <v>949</v>
       </c>
       <c r="F236" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="237" spans="1:6">
@@ -11452,7 +11452,7 @@
         <v>955</v>
       </c>
       <c r="C238" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D238" t="s">
         <v>956</v>
@@ -11461,7 +11461,7 @@
         <v>957</v>
       </c>
       <c r="F238" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="239" spans="1:6">
@@ -11472,7 +11472,7 @@
         <v>959</v>
       </c>
       <c r="C239" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D239" t="s">
         <v>960</v>
@@ -11481,7 +11481,7 @@
         <v>961</v>
       </c>
       <c r="F239" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="240" spans="1:6">
@@ -11501,7 +11501,7 @@
         <v>965</v>
       </c>
       <c r="F240" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="241" spans="1:6">
@@ -11512,7 +11512,7 @@
         <v>967</v>
       </c>
       <c r="C241" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D241" t="s">
         <v>968</v>
@@ -11521,7 +11521,7 @@
         <v>969</v>
       </c>
       <c r="F241" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="242" spans="1:6">
@@ -11532,7 +11532,7 @@
         <v>971</v>
       </c>
       <c r="C242" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D242" t="s">
         <v>972</v>
@@ -11561,7 +11561,7 @@
         <v>977</v>
       </c>
       <c r="F243" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="244" spans="1:6">
@@ -11592,7 +11592,7 @@
         <v>983</v>
       </c>
       <c r="C245" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D245" t="s">
         <v>984</v>
@@ -11621,7 +11621,7 @@
         <v>989</v>
       </c>
       <c r="F246" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="247" spans="1:6">
@@ -11652,7 +11652,7 @@
         <v>995</v>
       </c>
       <c r="C248" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D248" t="s">
         <v>996</v>
@@ -11661,7 +11661,7 @@
         <v>997</v>
       </c>
       <c r="F248" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="249" spans="1:6">
@@ -11692,7 +11692,7 @@
         <v>1003</v>
       </c>
       <c r="C250" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D250" t="s">
         <v>1004</v>
@@ -11701,7 +11701,7 @@
         <v>1005</v>
       </c>
       <c r="F250" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="251" spans="1:6">
@@ -11721,7 +11721,7 @@
         <v>1009</v>
       </c>
       <c r="F251" t="s">
-        <v>529</v>
+        <v>29</v>
       </c>
     </row>
     <row r="252" spans="1:6">
@@ -11752,7 +11752,7 @@
         <v>1015</v>
       </c>
       <c r="C253" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D253" t="s">
         <v>1016</v>
@@ -11761,7 +11761,7 @@
         <v>1017</v>
       </c>
       <c r="F253" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="254" spans="1:6">
@@ -11801,7 +11801,7 @@
         <v>1025</v>
       </c>
       <c r="F255" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="256" spans="1:6">
@@ -11852,7 +11852,7 @@
         <v>1035</v>
       </c>
       <c r="C258" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D258" t="s">
         <v>1036</v>
@@ -11861,7 +11861,7 @@
         <v>1037</v>
       </c>
       <c r="F258" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="259" spans="1:6">
@@ -11932,7 +11932,7 @@
         <v>1051</v>
       </c>
       <c r="C262" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D262" t="s">
         <v>1052</v>
@@ -11941,7 +11941,7 @@
         <v>1053</v>
       </c>
       <c r="F262" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="263" spans="1:6">
@@ -11981,7 +11981,7 @@
         <v>1061</v>
       </c>
       <c r="F264" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="265" spans="1:6">
@@ -12001,7 +12001,7 @@
         <v>1065</v>
       </c>
       <c r="F265" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="266" spans="1:6">
@@ -12012,7 +12012,7 @@
         <v>1067</v>
       </c>
       <c r="C266" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D266" t="s">
         <v>1068</v>
